--- a/Result/profitability/6185.xlsx
+++ b/Result/profitability/6185.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.005000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="N2" t="n">
-        <v>20.7825</v>
+        <v>23.755</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0675</v>
+        <v>0.07375</v>
       </c>
       <c r="N3" t="n">
-        <v>25.48</v>
+        <v>23.33625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0.12</v>
+        <v>0.1325</v>
       </c>
       <c r="N4" t="n">
-        <v>25.27</v>
+        <v>23.75</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.10625</v>
+        <v>0.1275</v>
       </c>
       <c r="N5" t="n">
-        <v>26.37875</v>
+        <v>24.1725</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>0.135</v>
+        <v>0.1275</v>
       </c>
       <c r="N6" t="n">
-        <v>26.28875</v>
+        <v>25.58125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.39</v>
       </c>
       <c r="M7" t="n">
-        <v>0.16125</v>
+        <v>0.1675</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1575</v>
+        <v>27.97125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>0.25125</v>
+        <v>0.28375</v>
       </c>
       <c r="N8" t="n">
-        <v>31.6675</v>
+        <v>31.98875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.365</v>
       </c>
       <c r="N9" t="n">
-        <v>35.55625</v>
+        <v>35.55625000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.53</v>
       </c>
       <c r="M13" t="n">
-        <v>0.70375</v>
+        <v>0.7037500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>39.69</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6185</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>195</v>
+      </c>
+      <c r="D75" t="n">
+        <v>166</v>
+      </c>
+      <c r="E75" t="n">
+        <v>28</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-15.70%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>53</v>
+      </c>
+      <c r="J75" t="n">
+        <v>23</v>
+      </c>
+      <c r="K75" t="n">
+        <v>18</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.857142857142857</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.569999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2148829431438126</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-17.65</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5484773151025482</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
